--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2193"/>
+  <dimension ref="A1:G2194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68370,6 +68370,37 @@
         </is>
       </c>
     </row>
+    <row r="2194">
+      <c r="A2194" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2194" s="4" t="n"/>
+      <c r="C2194" s="5" t="n">
+        <v>17.1277</v>
+      </c>
+      <c r="D2194" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2194" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2194" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2194" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2194"/>
+  <dimension ref="A1:G2195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68401,6 +68401,37 @@
         </is>
       </c>
     </row>
+    <row r="2195">
+      <c r="A2195" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2195" s="4" t="n"/>
+      <c r="C2195" s="7" t="n">
+        <v>17.1527</v>
+      </c>
+      <c r="D2195" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2195" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2195" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2195" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2195"/>
+  <dimension ref="A1:G2196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68432,6 +68432,37 @@
         </is>
       </c>
     </row>
+    <row r="2196">
+      <c r="A2196" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2196" s="4" t="n"/>
+      <c r="C2196" s="5" t="n">
+        <v>17.1872</v>
+      </c>
+      <c r="D2196" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2196" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2196" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2196" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2196"/>
+  <dimension ref="A1:G2197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68463,6 +68463,37 @@
         </is>
       </c>
     </row>
+    <row r="2197">
+      <c r="A2197" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2197" s="4" t="n"/>
+      <c r="C2197" s="7" t="n">
+        <v>17.245</v>
+      </c>
+      <c r="D2197" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2197" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2197" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2197" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2197"/>
+  <dimension ref="A1:G2198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68494,6 +68494,37 @@
         </is>
       </c>
     </row>
+    <row r="2198">
+      <c r="A2198" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2198" s="4" t="n"/>
+      <c r="C2198" s="5" t="n">
+        <v>17.2203</v>
+      </c>
+      <c r="D2198" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2198" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2198" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2198" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2198"/>
+  <dimension ref="A1:G2199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68525,6 +68525,37 @@
         </is>
       </c>
     </row>
+    <row r="2199">
+      <c r="A2199" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2199" s="4" t="n"/>
+      <c r="C2199" s="7" t="n">
+        <v>17.3015</v>
+      </c>
+      <c r="D2199" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2199" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2199" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2199" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2199"/>
+  <dimension ref="A1:G2200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68556,6 +68556,37 @@
         </is>
       </c>
     </row>
+    <row r="2200">
+      <c r="A2200" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2200" s="4" t="n"/>
+      <c r="C2200" s="5" t="n">
+        <v>17.503</v>
+      </c>
+      <c r="D2200" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2200" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2200" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2200" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2200"/>
+  <dimension ref="A1:G2201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68587,6 +68587,37 @@
         </is>
       </c>
     </row>
+    <row r="2201">
+      <c r="A2201" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B2201" s="4" t="n"/>
+      <c r="C2201" s="7" t="n">
+        <v>17.6425</v>
+      </c>
+      <c r="D2201" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2201" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2201" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2201" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2201"/>
+  <dimension ref="A1:G2202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68618,6 +68618,37 @@
         </is>
       </c>
     </row>
+    <row r="2202">
+      <c r="A2202" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B2202" s="4" t="n"/>
+      <c r="C2202" s="5" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="D2202" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2202" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2202" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2202" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2202"/>
+  <dimension ref="A1:G2203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68649,6 +68649,37 @@
         </is>
       </c>
     </row>
+    <row r="2203">
+      <c r="A2203" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B2203" s="4" t="n"/>
+      <c r="C2203" s="7" t="n">
+        <v>17.8413</v>
+      </c>
+      <c r="D2203" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2203" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2203" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2203" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2203"/>
+  <dimension ref="A1:G2204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68680,6 +68680,37 @@
         </is>
       </c>
     </row>
+    <row r="2204">
+      <c r="A2204" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B2204" s="4" t="n"/>
+      <c r="C2204" s="5" t="n">
+        <v>18.071</v>
+      </c>
+      <c r="D2204" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2204" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2204" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2204" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2204"/>
+  <dimension ref="A1:G2205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68711,6 +68711,37 @@
         </is>
       </c>
     </row>
+    <row r="2205">
+      <c r="A2205" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2205" s="4" t="n"/>
+      <c r="C2205" s="7" t="n">
+        <v>18.0692</v>
+      </c>
+      <c r="D2205" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2205" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2205" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2205" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2205"/>
+  <dimension ref="A1:G2206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68742,6 +68742,37 @@
         </is>
       </c>
     </row>
+    <row r="2206">
+      <c r="A2206" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2206" s="4" t="n"/>
+      <c r="C2206" s="5" t="n">
+        <v>18.3688</v>
+      </c>
+      <c r="D2206" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2206" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2206" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2206" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2206"/>
+  <dimension ref="A1:G2207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68773,6 +68773,37 @@
         </is>
       </c>
     </row>
+    <row r="2207">
+      <c r="A2207" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2207" s="4" t="n"/>
+      <c r="C2207" s="7" t="n">
+        <v>18.1903</v>
+      </c>
+      <c r="D2207" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2207" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2207" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2207" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2207"/>
+  <dimension ref="A1:G2208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68804,6 +68804,37 @@
         </is>
       </c>
     </row>
+    <row r="2208">
+      <c r="A2208" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B2208" s="4" t="n"/>
+      <c r="C2208" s="5" t="n">
+        <v>18.1343</v>
+      </c>
+      <c r="D2208" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2208" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2208" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2208" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2208"/>
+  <dimension ref="A1:G2209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68835,6 +68835,37 @@
         </is>
       </c>
     </row>
+    <row r="2209">
+      <c r="A2209" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2209" s="4" t="n"/>
+      <c r="C2209" s="7" t="n">
+        <v>17.967</v>
+      </c>
+      <c r="D2209" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2209" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2209" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2209" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2209"/>
+  <dimension ref="A1:G2210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68866,6 +68866,37 @@
         </is>
       </c>
     </row>
+    <row r="2210">
+      <c r="A2210" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2210" s="4" t="n"/>
+      <c r="C2210" s="5" t="n">
+        <v>17.978</v>
+      </c>
+      <c r="D2210" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2210" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2210" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2210" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2210"/>
+  <dimension ref="A1:G2211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68897,6 +68897,37 @@
         </is>
       </c>
     </row>
+    <row r="2211">
+      <c r="A2211" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2211" s="4" t="n"/>
+      <c r="C2211" s="7" t="n">
+        <v>18.1128</v>
+      </c>
+      <c r="D2211" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2211" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2211" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2211" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2211"/>
+  <dimension ref="A1:G2212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68928,6 +68928,37 @@
         </is>
       </c>
     </row>
+    <row r="2212">
+      <c r="A2212" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2212" s="4" t="n"/>
+      <c r="C2212" s="5" t="n">
+        <v>18.4163</v>
+      </c>
+      <c r="D2212" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2212" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2212" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2212" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2212"/>
+  <dimension ref="A1:G2213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68959,6 +68959,37 @@
         </is>
       </c>
     </row>
+    <row r="2213">
+      <c r="A2213" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2213" s="4" t="n"/>
+      <c r="C2213" s="7" t="n">
+        <v>18.2542</v>
+      </c>
+      <c r="D2213" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2213" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2213" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2213" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2213"/>
+  <dimension ref="A1:G2214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -68990,6 +68990,37 @@
         </is>
       </c>
     </row>
+    <row r="2214">
+      <c r="A2214" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2214" s="4" t="n"/>
+      <c r="C2214" s="5" t="n">
+        <v>18.3528</v>
+      </c>
+      <c r="D2214" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2214" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2214" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2214" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2214"/>
+  <dimension ref="A1:G2215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69021,6 +69021,37 @@
         </is>
       </c>
     </row>
+    <row r="2215">
+      <c r="A2215" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2215" s="4" t="n"/>
+      <c r="C2215" s="7" t="n">
+        <v>18.4888</v>
+      </c>
+      <c r="D2215" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2215" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2215" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2215" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2215"/>
+  <dimension ref="A1:G2216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69052,6 +69052,37 @@
         </is>
       </c>
     </row>
+    <row r="2216">
+      <c r="A2216" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2216" s="4" t="n"/>
+      <c r="C2216" s="5" t="n">
+        <v>18.425</v>
+      </c>
+      <c r="D2216" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2216" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2216" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2216" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2216"/>
+  <dimension ref="A1:G2217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69083,6 +69083,37 @@
         </is>
       </c>
     </row>
+    <row r="2217">
+      <c r="A2217" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2217" s="4" t="n"/>
+      <c r="C2217" s="7" t="n">
+        <v>18.493</v>
+      </c>
+      <c r="D2217" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2217" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2217" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2217" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2217"/>
+  <dimension ref="A1:G2218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69114,6 +69114,37 @@
         </is>
       </c>
     </row>
+    <row r="2218">
+      <c r="A2218" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2218" s="4" t="n"/>
+      <c r="C2218" s="5" t="n">
+        <v>18.4253</v>
+      </c>
+      <c r="D2218" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2218" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2218" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2218" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2218"/>
+  <dimension ref="A1:G2219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69145,6 +69145,37 @@
         </is>
       </c>
     </row>
+    <row r="2219">
+      <c r="A2219" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2219" s="4" t="n"/>
+      <c r="C2219" s="7" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="D2219" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2219" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2219" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2219" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2219"/>
+  <dimension ref="A1:G2220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69176,6 +69176,37 @@
         </is>
       </c>
     </row>
+    <row r="2220">
+      <c r="A2220" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2220" s="4" t="n"/>
+      <c r="C2220" s="5" t="n">
+        <v>18.6425</v>
+      </c>
+      <c r="D2220" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2220" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2220" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2220" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2220"/>
+  <dimension ref="A1:G2221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69207,6 +69207,37 @@
         </is>
       </c>
     </row>
+    <row r="2221">
+      <c r="A2221" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2221" s="4" t="n"/>
+      <c r="C2221" s="7" t="n">
+        <v>18.7005</v>
+      </c>
+      <c r="D2221" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2221" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2221" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2221" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2221"/>
+  <dimension ref="A1:G2222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69238,6 +69238,37 @@
         </is>
       </c>
     </row>
+    <row r="2222">
+      <c r="A2222" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2222" s="4" t="n"/>
+      <c r="C2222" s="5" t="n">
+        <v>18.667</v>
+      </c>
+      <c r="D2222" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2222" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2222" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2222" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2222"/>
+  <dimension ref="A1:G2223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69269,6 +69269,37 @@
         </is>
       </c>
     </row>
+    <row r="2223">
+      <c r="A2223" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2223" s="4" t="n"/>
+      <c r="C2223" s="7" t="n">
+        <v>18.5798</v>
+      </c>
+      <c r="D2223" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2223" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2223" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2223" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2223"/>
+  <dimension ref="A1:G2224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69300,6 +69300,37 @@
         </is>
       </c>
     </row>
+    <row r="2224">
+      <c r="A2224" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2224" s="4" t="n"/>
+      <c r="C2224" s="5" t="n">
+        <v>18.6525</v>
+      </c>
+      <c r="D2224" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2224" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2224" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2224" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2224"/>
+  <dimension ref="A1:G2225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69331,6 +69331,37 @@
         </is>
       </c>
     </row>
+    <row r="2225">
+      <c r="A2225" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2225" s="4" t="n"/>
+      <c r="C2225" s="7" t="n">
+        <v>18.6673</v>
+      </c>
+      <c r="D2225" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2225" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2225" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2225" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2225"/>
+  <dimension ref="A1:G2226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69362,6 +69362,37 @@
         </is>
       </c>
     </row>
+    <row r="2226">
+      <c r="A2226" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2226" s="4" t="n"/>
+      <c r="C2226" s="5" t="n">
+        <v>18.8148</v>
+      </c>
+      <c r="D2226" s="6" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2226" s="6" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2226" s="6" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2226" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
+++ b/downloads/indicadores/TIPOCAMBIO/TIPOCAMBIO_datos.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2226"/>
+  <dimension ref="A1:G2227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -69393,6 +69393,37 @@
         </is>
       </c>
     </row>
+    <row r="2227">
+      <c r="A2227" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2227" s="4" t="n"/>
+      <c r="C2227" s="7" t="n">
+        <v>18.7962</v>
+      </c>
+      <c r="D2227" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E2227" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F2227" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+      <c r="G2227" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
